--- a/Mision2/proyecto_tkinter_ia_excel/ejemplo.xlsx
+++ b/Mision2/proyecto_tkinter_ia_excel/ejemplo.xlsx
@@ -455,12 +455,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1234567 Juan</t>
+          <t>1234567</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1234567</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Juan 1234567</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2333434</t>
+          <t>234242</t>
         </is>
       </c>
     </row>
@@ -477,12 +487,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>987654 Maria</t>
+          <t>987654</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>987654</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Maria 987654</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4545</t>
+          <t>1241</t>
         </is>
       </c>
     </row>
